--- a/research/traditional_assets/database/data/latvia/latvia_food_processing.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_food_processing.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0479</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="E2">
-        <v>0.261</v>
+        <v>-0.00651</v>
       </c>
       <c r="G2">
-        <v>0.1373417721518987</v>
+        <v>0.1306122448979592</v>
       </c>
       <c r="H2">
-        <v>0.1373417721518987</v>
+        <v>0.1306122448979592</v>
       </c>
       <c r="I2">
-        <v>0.09620253164556962</v>
+        <v>0.07414965986394557</v>
       </c>
       <c r="J2">
-        <v>0.09409590686500971</v>
+        <v>0.07112314313480493</v>
       </c>
       <c r="K2">
-        <v>0.133</v>
+        <v>0.094</v>
       </c>
       <c r="L2">
-        <v>0.08417721518987342</v>
+        <v>0.06394557823129252</v>
       </c>
       <c r="M2">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="N2">
-        <v>0.01815068493150685</v>
+        <v>0.01050955414012739</v>
       </c>
       <c r="O2">
-        <v>0.3984962406015037</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="P2">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="Q2">
-        <v>0.01815068493150685</v>
+        <v>0.01050955414012739</v>
       </c>
       <c r="R2">
-        <v>0.3984962406015037</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.278</v>
+        <v>0.249</v>
       </c>
       <c r="V2">
-        <v>0.09520547945205481</v>
+        <v>0.07929936305732484</v>
       </c>
       <c r="W2">
-        <v>0.06927083333333334</v>
+        <v>0.04771573604060914</v>
       </c>
       <c r="X2">
-        <v>0.05496804879322961</v>
+        <v>0.09421336292138363</v>
       </c>
       <c r="Y2">
-        <v>0.01430278454010373</v>
+        <v>-0.0464976268807745</v>
       </c>
       <c r="Z2">
-        <v>0.9599027946537061</v>
+        <v>0.8687943262411347</v>
       </c>
       <c r="AA2">
-        <v>0.09032292396519766</v>
+        <v>0.06179138321995465</v>
       </c>
       <c r="AB2">
-        <v>0.05496804879322961</v>
+        <v>0.09421336292138363</v>
       </c>
       <c r="AC2">
-        <v>0.03535487517196805</v>
+        <v>-0.03242197970142898</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.278</v>
+        <v>-0.249</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.105223315669947</v>
+        <v>-0.0861293670010377</v>
       </c>
       <c r="AK2">
-        <v>-0.1643026004728133</v>
+        <v>-0.1681296421336935</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.269406392694064</v>
+        <v>-1.606451612903226</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0479</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="E3">
-        <v>0.261</v>
+        <v>-0.00651</v>
       </c>
       <c r="G3">
-        <v>0.1373417721518987</v>
+        <v>0.1306122448979592</v>
       </c>
       <c r="H3">
-        <v>0.1373417721518987</v>
+        <v>0.1306122448979592</v>
       </c>
       <c r="I3">
-        <v>0.09620253164556962</v>
+        <v>0.07414965986394557</v>
       </c>
       <c r="J3">
-        <v>0.09409590686500971</v>
+        <v>0.07112314313480493</v>
       </c>
       <c r="K3">
-        <v>0.133</v>
+        <v>0.094</v>
       </c>
       <c r="L3">
-        <v>0.08417721518987342</v>
+        <v>0.06394557823129252</v>
       </c>
       <c r="M3">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="N3">
-        <v>0.01815068493150685</v>
+        <v>0.01050955414012739</v>
       </c>
       <c r="O3">
-        <v>0.3984962406015037</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="P3">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="Q3">
-        <v>0.01815068493150685</v>
+        <v>0.01050955414012739</v>
       </c>
       <c r="R3">
-        <v>0.3984962406015037</v>
+        <v>0.351063829787234</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.278</v>
+        <v>0.249</v>
       </c>
       <c r="V3">
-        <v>0.09520547945205481</v>
+        <v>0.07929936305732484</v>
       </c>
       <c r="W3">
-        <v>0.06927083333333334</v>
+        <v>0.04771573604060914</v>
       </c>
       <c r="X3">
-        <v>0.05496804879322961</v>
+        <v>0.09421336292138363</v>
       </c>
       <c r="Y3">
-        <v>0.01430278454010373</v>
+        <v>-0.0464976268807745</v>
       </c>
       <c r="Z3">
-        <v>0.9599027946537061</v>
+        <v>0.8687943262411347</v>
       </c>
       <c r="AA3">
-        <v>0.09032292396519766</v>
+        <v>0.06179138321995465</v>
       </c>
       <c r="AB3">
-        <v>0.05496804879322961</v>
+        <v>0.09421336292138363</v>
       </c>
       <c r="AC3">
-        <v>0.03535487517196805</v>
+        <v>-0.03242197970142898</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.278</v>
+        <v>-0.249</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.105223315669947</v>
+        <v>-0.0861293670010377</v>
       </c>
       <c r="AK3">
-        <v>-0.1643026004728133</v>
+        <v>-0.1681296421336935</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.269406392694064</v>
+        <v>-1.606451612903226</v>
       </c>
     </row>
   </sheetData>
